--- a/athlete_forms/012_player_registration_form--athlete_forms.xlsx
+++ b/athlete_forms/012_player_registration_form--athlete_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -633,7 +633,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Player Info</t>
+          <t>Player Info Update</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -656,7 +656,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Contact Info</t>
+          <t>Contact Info Update</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -679,7 +679,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Player Photo</t>
+          <t>Player Photo Update</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -702,7 +702,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Team Choice</t>
+          <t>Team Choice Update</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -752,7 +752,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Player Name</t>
+          <t>Player Name Update</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -802,7 +802,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Player DOB</t>
+          <t>Player Dob Update</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -852,7 +852,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Player Phone</t>
+          <t>Player Phone Update</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -902,7 +902,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Player Email</t>
+          <t>Player Email Update</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Team Email</t>
+          <t>Team Email Update</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Team Phone</t>
+          <t>Team Phone Update</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Player Address</t>
+          <t>Player Address Update</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Team Address</t>
+          <t>Team Address Update</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
